--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127905051</v>
       </c>
       <c r="B2" t="n">
-        <v>56585</v>
+        <v>56612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,1168 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128923517</v>
+      </c>
+      <c r="B3" t="n">
+        <v>86959</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>726207</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6385429</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128923524</v>
+      </c>
+      <c r="B4" t="n">
+        <v>87016</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>433</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>726121</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6385220</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128923519</v>
+      </c>
+      <c r="B5" t="n">
+        <v>86959</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>726201</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6385293</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128923521</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98654</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>726187</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6385421</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128923514</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92808</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>726206</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6385308</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128923516</v>
+      </c>
+      <c r="B8" t="n">
+        <v>86959</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>726321</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6385413</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128923518</v>
+      </c>
+      <c r="B9" t="n">
+        <v>86959</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>726205</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6385310</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128923520</v>
+      </c>
+      <c r="B10" t="n">
+        <v>86959</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>726122</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6385222</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128923525</v>
+      </c>
+      <c r="B11" t="n">
+        <v>86784</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>726310</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6385406</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128923526</v>
+      </c>
+      <c r="B12" t="n">
+        <v>86784</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>726201</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6385286</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128923528</v>
+      </c>
+      <c r="B13" t="n">
+        <v>86784</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>726191</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6385286</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128923530</v>
+      </c>
+      <c r="B14" t="n">
+        <v>86922</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>726161</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6385253</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -1280,32 +1280,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128923516</v>
+        <v>128923525</v>
       </c>
       <c r="B8" t="n">
-        <v>86959</v>
+        <v>86784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726321</v>
+        <v>726310</v>
       </c>
       <c r="R8" t="n">
-        <v>6385413</v>
+        <v>6385406</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1359,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1378,7 +1377,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128923518</v>
+        <v>128923516</v>
       </c>
       <c r="B9" t="n">
         <v>86959</v>
@@ -1413,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726205</v>
+        <v>726321</v>
       </c>
       <c r="R9" t="n">
-        <v>6385310</v>
+        <v>6385413</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,7 +1475,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128923520</v>
+        <v>128923518</v>
       </c>
       <c r="B10" t="n">
         <v>86959</v>
@@ -1511,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726122</v>
+        <v>726205</v>
       </c>
       <c r="R10" t="n">
-        <v>6385222</v>
+        <v>6385310</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,32 +1573,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128923525</v>
+        <v>128923520</v>
       </c>
       <c r="B11" t="n">
-        <v>86784</v>
+        <v>86959</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726310</v>
+        <v>726122</v>
       </c>
       <c r="R11" t="n">
-        <v>6385406</v>
+        <v>6385222</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,6 +1652,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127905051</v>
       </c>
       <c r="B2" t="n">
-        <v>56612</v>
+        <v>56615</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,34 +800,30 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128923517</v>
+        <v>128923524</v>
       </c>
       <c r="B3" t="n">
-        <v>86959</v>
+        <v>87020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>726207</v>
+        <v>726121</v>
       </c>
       <c r="R3" t="n">
-        <v>6385429</v>
+        <v>6385220</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,30 +894,34 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128923524</v>
+        <v>128923517</v>
       </c>
       <c r="B4" t="n">
-        <v>87016</v>
+        <v>86963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>726121</v>
+        <v>726207</v>
       </c>
       <c r="R4" t="n">
-        <v>6385220</v>
+        <v>6385429</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +995,7 @@
         <v>128923519</v>
       </c>
       <c r="B5" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128923521</v>
       </c>
       <c r="B6" t="n">
-        <v>98654</v>
+        <v>98658</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128923514</v>
       </c>
       <c r="B7" t="n">
-        <v>92808</v>
+        <v>92812</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,32 +1280,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128923525</v>
+        <v>128923516</v>
       </c>
       <c r="B8" t="n">
-        <v>86784</v>
+        <v>86963</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726310</v>
+        <v>726321</v>
       </c>
       <c r="R8" t="n">
-        <v>6385406</v>
+        <v>6385413</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,6 +1359,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1377,10 +1378,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128923516</v>
+        <v>128923518</v>
       </c>
       <c r="B9" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1412,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726321</v>
+        <v>726205</v>
       </c>
       <c r="R9" t="n">
-        <v>6385413</v>
+        <v>6385310</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128923518</v>
+        <v>128923520</v>
       </c>
       <c r="B10" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1510,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726205</v>
+        <v>726122</v>
       </c>
       <c r="R10" t="n">
-        <v>6385310</v>
+        <v>6385222</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,32 +1574,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128923520</v>
+        <v>128923525</v>
       </c>
       <c r="B11" t="n">
-        <v>86959</v>
+        <v>86788</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726122</v>
+        <v>726310</v>
       </c>
       <c r="R11" t="n">
-        <v>6385222</v>
+        <v>6385406</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1652,7 +1653,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>128923526</v>
       </c>
       <c r="B12" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>128923528</v>
       </c>
       <c r="B13" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>128923530</v>
       </c>
       <c r="B14" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -1280,7 +1280,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128923516</v>
+        <v>128923518</v>
       </c>
       <c r="B8" t="n">
         <v>86963</v>
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726321</v>
+        <v>726205</v>
       </c>
       <c r="R8" t="n">
-        <v>6385413</v>
+        <v>6385310</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128923518</v>
+        <v>128923516</v>
       </c>
       <c r="B9" t="n">
         <v>86963</v>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726205</v>
+        <v>726321</v>
       </c>
       <c r="R9" t="n">
-        <v>6385310</v>
+        <v>6385413</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -1280,32 +1280,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128923518</v>
+        <v>128923525</v>
       </c>
       <c r="B8" t="n">
-        <v>86963</v>
+        <v>86788</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726205</v>
+        <v>726310</v>
       </c>
       <c r="R8" t="n">
-        <v>6385310</v>
+        <v>6385406</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1359,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1378,7 +1377,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128923516</v>
+        <v>128923518</v>
       </c>
       <c r="B9" t="n">
         <v>86963</v>
@@ -1413,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726321</v>
+        <v>726205</v>
       </c>
       <c r="R9" t="n">
-        <v>6385413</v>
+        <v>6385310</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,7 +1475,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128923520</v>
+        <v>128923516</v>
       </c>
       <c r="B10" t="n">
         <v>86963</v>
@@ -1511,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726122</v>
+        <v>726321</v>
       </c>
       <c r="R10" t="n">
-        <v>6385222</v>
+        <v>6385413</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,32 +1573,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128923525</v>
+        <v>128923520</v>
       </c>
       <c r="B11" t="n">
-        <v>86788</v>
+        <v>86963</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726310</v>
+        <v>726122</v>
       </c>
       <c r="R11" t="n">
-        <v>6385406</v>
+        <v>6385222</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,6 +1652,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127905051</v>
       </c>
       <c r="B2" t="n">
-        <v>56615</v>
+        <v>56618</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>128923524</v>
       </c>
       <c r="B3" t="n">
-        <v>87020</v>
+        <v>87025</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128923517</v>
       </c>
       <c r="B4" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>128923519</v>
       </c>
       <c r="B5" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128923521</v>
       </c>
       <c r="B6" t="n">
-        <v>98658</v>
+        <v>98665</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128923514</v>
       </c>
       <c r="B7" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128923525</v>
       </c>
       <c r="B8" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,10 +1377,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128923518</v>
+        <v>128923516</v>
       </c>
       <c r="B9" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726205</v>
+        <v>726321</v>
       </c>
       <c r="R9" t="n">
-        <v>6385310</v>
+        <v>6385413</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128923516</v>
+        <v>128923518</v>
       </c>
       <c r="B10" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726321</v>
+        <v>726205</v>
       </c>
       <c r="R10" t="n">
-        <v>6385413</v>
+        <v>6385310</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
         <v>128923520</v>
       </c>
       <c r="B11" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>128923526</v>
       </c>
       <c r="B12" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>128923528</v>
       </c>
       <c r="B13" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>128923530</v>
       </c>
       <c r="B14" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -1280,32 +1280,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128923518</v>
+        <v>128923525</v>
       </c>
       <c r="B8" t="n">
-        <v>86975</v>
+        <v>86800</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726205</v>
+        <v>726310</v>
       </c>
       <c r="R8" t="n">
-        <v>6385310</v>
+        <v>6385406</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1359,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1378,7 +1377,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128923520</v>
+        <v>128923518</v>
       </c>
       <c r="B9" t="n">
         <v>86975</v>
@@ -1413,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726122</v>
+        <v>726205</v>
       </c>
       <c r="R9" t="n">
-        <v>6385222</v>
+        <v>6385310</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,7 +1475,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128923516</v>
+        <v>128923520</v>
       </c>
       <c r="B10" t="n">
         <v>86975</v>
@@ -1511,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726321</v>
+        <v>726122</v>
       </c>
       <c r="R10" t="n">
-        <v>6385413</v>
+        <v>6385222</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,32 +1573,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128923525</v>
+        <v>128923516</v>
       </c>
       <c r="B11" t="n">
-        <v>86800</v>
+        <v>86975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726310</v>
+        <v>726321</v>
       </c>
       <c r="R11" t="n">
-        <v>6385406</v>
+        <v>6385413</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,6 +1652,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -800,34 +800,30 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128923517</v>
+        <v>128923524</v>
       </c>
       <c r="B3" t="n">
-        <v>86975</v>
+        <v>87035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>726207</v>
+        <v>726121</v>
       </c>
       <c r="R3" t="n">
-        <v>6385429</v>
+        <v>6385220</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,30 +894,34 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128923524</v>
+        <v>128923517</v>
       </c>
       <c r="B4" t="n">
-        <v>87032</v>
+        <v>86978</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>726121</v>
+        <v>726207</v>
       </c>
       <c r="R4" t="n">
-        <v>6385220</v>
+        <v>6385429</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +995,7 @@
         <v>128923519</v>
       </c>
       <c r="B5" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128923521</v>
       </c>
       <c r="B6" t="n">
-        <v>98673</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128923514</v>
       </c>
       <c r="B7" t="n">
-        <v>92825</v>
+        <v>92830</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128923525</v>
       </c>
       <c r="B8" t="n">
-        <v>86800</v>
+        <v>86803</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>128923518</v>
       </c>
       <c r="B9" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128923520</v>
       </c>
       <c r="B10" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>128923516</v>
       </c>
       <c r="B11" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>128923526</v>
       </c>
       <c r="B12" t="n">
-        <v>86800</v>
+        <v>86803</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>128923528</v>
       </c>
       <c r="B13" t="n">
-        <v>86800</v>
+        <v>86803</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>128923530</v>
       </c>
       <c r="B14" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128923524</v>
       </c>
       <c r="B3" t="n">
-        <v>87035</v>
+        <v>87038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128923517</v>
       </c>
       <c r="B4" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>128923519</v>
       </c>
       <c r="B5" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128923521</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98681</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128923514</v>
       </c>
       <c r="B7" t="n">
-        <v>92830</v>
+        <v>92833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,32 +1280,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128923525</v>
+        <v>128923516</v>
       </c>
       <c r="B8" t="n">
-        <v>86803</v>
+        <v>86981</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726310</v>
+        <v>726321</v>
       </c>
       <c r="R8" t="n">
-        <v>6385406</v>
+        <v>6385413</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,6 +1359,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1380,7 +1381,7 @@
         <v>128923518</v>
       </c>
       <c r="B9" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1479,7 @@
         <v>128923520</v>
       </c>
       <c r="B10" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,32 +1574,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128923516</v>
+        <v>128923525</v>
       </c>
       <c r="B11" t="n">
-        <v>86978</v>
+        <v>86806</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726321</v>
+        <v>726310</v>
       </c>
       <c r="R11" t="n">
-        <v>6385413</v>
+        <v>6385406</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1652,7 +1653,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>128923526</v>
       </c>
       <c r="B12" t="n">
-        <v>86803</v>
+        <v>86806</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>128923528</v>
       </c>
       <c r="B13" t="n">
-        <v>86803</v>
+        <v>86806</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>128923530</v>
       </c>
       <c r="B14" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -1280,7 +1280,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128923516</v>
+        <v>128923518</v>
       </c>
       <c r="B8" t="n">
         <v>86981</v>
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726321</v>
+        <v>726205</v>
       </c>
       <c r="R8" t="n">
-        <v>6385413</v>
+        <v>6385310</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128923518</v>
+        <v>128923520</v>
       </c>
       <c r="B9" t="n">
         <v>86981</v>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726205</v>
+        <v>726122</v>
       </c>
       <c r="R9" t="n">
-        <v>6385310</v>
+        <v>6385222</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,7 +1476,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128923520</v>
+        <v>128923516</v>
       </c>
       <c r="B10" t="n">
         <v>86981</v>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726122</v>
+        <v>726321</v>
       </c>
       <c r="R10" t="n">
-        <v>6385222</v>
+        <v>6385413</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -800,30 +800,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128923524</v>
+        <v>128923517</v>
       </c>
       <c r="B3" t="n">
-        <v>87038</v>
+        <v>86981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>726121</v>
+        <v>726207</v>
       </c>
       <c r="R3" t="n">
-        <v>6385220</v>
+        <v>6385429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,34 +898,30 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128923517</v>
+        <v>128923524</v>
       </c>
       <c r="B4" t="n">
-        <v>86981</v>
+        <v>87038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>726207</v>
+        <v>726121</v>
       </c>
       <c r="R4" t="n">
-        <v>6385429</v>
+        <v>6385220</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1280,32 +1280,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128923518</v>
+        <v>128923525</v>
       </c>
       <c r="B8" t="n">
-        <v>86981</v>
+        <v>86806</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726205</v>
+        <v>726310</v>
       </c>
       <c r="R8" t="n">
-        <v>6385310</v>
+        <v>6385406</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1359,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1378,7 +1377,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128923520</v>
+        <v>128923516</v>
       </c>
       <c r="B9" t="n">
         <v>86981</v>
@@ -1413,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726122</v>
+        <v>726321</v>
       </c>
       <c r="R9" t="n">
-        <v>6385222</v>
+        <v>6385413</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,7 +1475,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128923516</v>
+        <v>128923518</v>
       </c>
       <c r="B10" t="n">
         <v>86981</v>
@@ -1511,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726321</v>
+        <v>726205</v>
       </c>
       <c r="R10" t="n">
-        <v>6385413</v>
+        <v>6385310</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,32 +1573,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128923525</v>
+        <v>128923520</v>
       </c>
       <c r="B11" t="n">
-        <v>86806</v>
+        <v>86981</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726310</v>
+        <v>726122</v>
       </c>
       <c r="R11" t="n">
-        <v>6385406</v>
+        <v>6385222</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,6 +1652,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127905051</v>
       </c>
       <c r="B2" t="n">
-        <v>56618</v>
+        <v>56620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>128923517</v>
       </c>
       <c r="B3" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>128923524</v>
       </c>
       <c r="B4" t="n">
-        <v>87038</v>
+        <v>87042</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>128923519</v>
       </c>
       <c r="B5" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128923521</v>
       </c>
       <c r="B6" t="n">
-        <v>98681</v>
+        <v>98691</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128923514</v>
       </c>
       <c r="B7" t="n">
-        <v>92833</v>
+        <v>92840</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,32 +1280,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128923525</v>
+        <v>128923516</v>
       </c>
       <c r="B8" t="n">
-        <v>86806</v>
+        <v>86985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726310</v>
+        <v>726321</v>
       </c>
       <c r="R8" t="n">
-        <v>6385406</v>
+        <v>6385413</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,6 +1359,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1377,10 +1378,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128923516</v>
+        <v>128923518</v>
       </c>
       <c r="B9" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1412,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726321</v>
+        <v>726205</v>
       </c>
       <c r="R9" t="n">
-        <v>6385413</v>
+        <v>6385310</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128923518</v>
+        <v>128923520</v>
       </c>
       <c r="B10" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1510,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726205</v>
+        <v>726122</v>
       </c>
       <c r="R10" t="n">
-        <v>6385310</v>
+        <v>6385222</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,32 +1574,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128923520</v>
+        <v>128923525</v>
       </c>
       <c r="B11" t="n">
-        <v>86981</v>
+        <v>86810</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726122</v>
+        <v>726310</v>
       </c>
       <c r="R11" t="n">
-        <v>6385222</v>
+        <v>6385406</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1652,7 +1653,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>128923526</v>
       </c>
       <c r="B12" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>128923528</v>
       </c>
       <c r="B13" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>128923530</v>
       </c>
       <c r="B14" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -800,34 +800,30 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128923517</v>
+        <v>128923524</v>
       </c>
       <c r="B3" t="n">
-        <v>86985</v>
+        <v>87042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>726207</v>
+        <v>726121</v>
       </c>
       <c r="R3" t="n">
-        <v>6385429</v>
+        <v>6385220</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,30 +894,34 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128923524</v>
+        <v>128923517</v>
       </c>
       <c r="B4" t="n">
-        <v>87042</v>
+        <v>86985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>726121</v>
+        <v>726207</v>
       </c>
       <c r="R4" t="n">
-        <v>6385220</v>
+        <v>6385429</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128923526</v>
+        <v>128923528</v>
       </c>
       <c r="B12" t="n">
         <v>86810</v>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>726201</v>
+        <v>726191</v>
       </c>
       <c r="R12" t="n">
         <v>6385286</v>
@@ -1768,7 +1768,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128923528</v>
+        <v>128923526</v>
       </c>
       <c r="B13" t="n">
         <v>86810</v>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>726191</v>
+        <v>726201</v>
       </c>
       <c r="R13" t="n">
         <v>6385286</v>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128923524</v>
       </c>
       <c r="B3" t="n">
-        <v>87042</v>
+        <v>87049</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128923517</v>
       </c>
       <c r="B4" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>128923519</v>
       </c>
       <c r="B5" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128923521</v>
       </c>
       <c r="B6" t="n">
-        <v>98691</v>
+        <v>98698</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128923514</v>
       </c>
       <c r="B7" t="n">
-        <v>92840</v>
+        <v>92847</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,32 +1280,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128923516</v>
+        <v>128923525</v>
       </c>
       <c r="B8" t="n">
-        <v>86985</v>
+        <v>86817</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726321</v>
+        <v>726310</v>
       </c>
       <c r="R8" t="n">
-        <v>6385413</v>
+        <v>6385406</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1359,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1378,10 +1377,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128923518</v>
+        <v>128923516</v>
       </c>
       <c r="B9" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726205</v>
+        <v>726321</v>
       </c>
       <c r="R9" t="n">
-        <v>6385310</v>
+        <v>6385413</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128923520</v>
+        <v>128923518</v>
       </c>
       <c r="B10" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726122</v>
+        <v>726205</v>
       </c>
       <c r="R10" t="n">
-        <v>6385222</v>
+        <v>6385310</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,32 +1573,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128923525</v>
+        <v>128923520</v>
       </c>
       <c r="B11" t="n">
-        <v>86810</v>
+        <v>86992</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726310</v>
+        <v>726122</v>
       </c>
       <c r="R11" t="n">
-        <v>6385406</v>
+        <v>6385222</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,6 +1652,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1671,10 +1671,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128923528</v>
+        <v>128923526</v>
       </c>
       <c r="B12" t="n">
-        <v>86810</v>
+        <v>86817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>726191</v>
+        <v>726201</v>
       </c>
       <c r="R12" t="n">
         <v>6385286</v>
@@ -1768,10 +1768,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128923526</v>
+        <v>128923528</v>
       </c>
       <c r="B13" t="n">
-        <v>86810</v>
+        <v>86817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>726201</v>
+        <v>726191</v>
       </c>
       <c r="R13" t="n">
         <v>6385286</v>
@@ -1868,7 +1868,7 @@
         <v>128923530</v>
       </c>
       <c r="B14" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128923524</v>
       </c>
       <c r="B3" t="n">
-        <v>87049</v>
+        <v>87051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128923517</v>
       </c>
       <c r="B4" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>128923519</v>
       </c>
       <c r="B5" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128923521</v>
       </c>
       <c r="B6" t="n">
-        <v>98698</v>
+        <v>98700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128923514</v>
       </c>
       <c r="B7" t="n">
-        <v>92847</v>
+        <v>92849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128923525</v>
       </c>
       <c r="B8" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>128923516</v>
       </c>
       <c r="B9" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128923518</v>
       </c>
       <c r="B10" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>128923520</v>
       </c>
       <c r="B11" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>128923526</v>
       </c>
       <c r="B12" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>128923528</v>
       </c>
       <c r="B13" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>128923530</v>
       </c>
       <c r="B14" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -1280,32 +1280,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128923525</v>
+        <v>128923516</v>
       </c>
       <c r="B8" t="n">
-        <v>86819</v>
+        <v>86994</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726310</v>
+        <v>726321</v>
       </c>
       <c r="R8" t="n">
-        <v>6385406</v>
+        <v>6385413</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,6 +1359,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1377,7 +1378,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128923516</v>
+        <v>128923518</v>
       </c>
       <c r="B9" t="n">
         <v>86994</v>
@@ -1412,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726321</v>
+        <v>726205</v>
       </c>
       <c r="R9" t="n">
-        <v>6385413</v>
+        <v>6385310</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,7 +1476,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128923518</v>
+        <v>128923520</v>
       </c>
       <c r="B10" t="n">
         <v>86994</v>
@@ -1510,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726205</v>
+        <v>726122</v>
       </c>
       <c r="R10" t="n">
-        <v>6385310</v>
+        <v>6385222</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,32 +1574,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128923520</v>
+        <v>128923525</v>
       </c>
       <c r="B11" t="n">
-        <v>86994</v>
+        <v>86819</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726122</v>
+        <v>726310</v>
       </c>
       <c r="R11" t="n">
-        <v>6385222</v>
+        <v>6385406</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1652,7 +1653,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -1280,32 +1280,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128923516</v>
+        <v>128923525</v>
       </c>
       <c r="B8" t="n">
-        <v>86994</v>
+        <v>86819</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726321</v>
+        <v>726310</v>
       </c>
       <c r="R8" t="n">
-        <v>6385413</v>
+        <v>6385406</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1359,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1378,7 +1377,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128923518</v>
+        <v>128923516</v>
       </c>
       <c r="B9" t="n">
         <v>86994</v>
@@ -1413,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726205</v>
+        <v>726321</v>
       </c>
       <c r="R9" t="n">
-        <v>6385310</v>
+        <v>6385413</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,7 +1475,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128923520</v>
+        <v>128923518</v>
       </c>
       <c r="B10" t="n">
         <v>86994</v>
@@ -1511,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726122</v>
+        <v>726205</v>
       </c>
       <c r="R10" t="n">
-        <v>6385222</v>
+        <v>6385310</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,32 +1573,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128923525</v>
+        <v>128923520</v>
       </c>
       <c r="B11" t="n">
-        <v>86819</v>
+        <v>86994</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726310</v>
+        <v>726122</v>
       </c>
       <c r="R11" t="n">
-        <v>6385406</v>
+        <v>6385222</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,6 +1652,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -800,30 +800,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128923524</v>
+        <v>128923517</v>
       </c>
       <c r="B3" t="n">
-        <v>87051</v>
+        <v>86995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>726121</v>
+        <v>726207</v>
       </c>
       <c r="R3" t="n">
-        <v>6385220</v>
+        <v>6385429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,34 +898,30 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128923517</v>
+        <v>128923524</v>
       </c>
       <c r="B4" t="n">
-        <v>86994</v>
+        <v>87052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>726207</v>
+        <v>726121</v>
       </c>
       <c r="R4" t="n">
-        <v>6385429</v>
+        <v>6385220</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +995,7 @@
         <v>128923519</v>
       </c>
       <c r="B5" t="n">
-        <v>86994</v>
+        <v>86995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128923521</v>
       </c>
       <c r="B6" t="n">
-        <v>98700</v>
+        <v>98726</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128923514</v>
       </c>
       <c r="B7" t="n">
-        <v>92849</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128923525</v>
       </c>
       <c r="B8" t="n">
-        <v>86819</v>
+        <v>86820</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,10 +1377,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128923516</v>
+        <v>128923518</v>
       </c>
       <c r="B9" t="n">
-        <v>86994</v>
+        <v>86995</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726321</v>
+        <v>726205</v>
       </c>
       <c r="R9" t="n">
-        <v>6385413</v>
+        <v>6385310</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128923518</v>
+        <v>128923520</v>
       </c>
       <c r="B10" t="n">
-        <v>86994</v>
+        <v>86995</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726205</v>
+        <v>726122</v>
       </c>
       <c r="R10" t="n">
-        <v>6385310</v>
+        <v>6385222</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128923520</v>
+        <v>128923516</v>
       </c>
       <c r="B11" t="n">
-        <v>86994</v>
+        <v>86995</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726122</v>
+        <v>726321</v>
       </c>
       <c r="R11" t="n">
-        <v>6385222</v>
+        <v>6385413</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
         <v>128923526</v>
       </c>
       <c r="B12" t="n">
-        <v>86819</v>
+        <v>86820</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>128923528</v>
       </c>
       <c r="B13" t="n">
-        <v>86819</v>
+        <v>86820</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>128923530</v>
       </c>
       <c r="B14" t="n">
-        <v>86957</v>
+        <v>86958</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -800,34 +800,30 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128923517</v>
+        <v>128923524</v>
       </c>
       <c r="B3" t="n">
-        <v>86995</v>
+        <v>87052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>726207</v>
+        <v>726121</v>
       </c>
       <c r="R3" t="n">
-        <v>6385429</v>
+        <v>6385220</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,30 +894,34 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128923524</v>
+        <v>128923517</v>
       </c>
       <c r="B4" t="n">
-        <v>87052</v>
+        <v>86995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>726121</v>
+        <v>726207</v>
       </c>
       <c r="R4" t="n">
-        <v>6385220</v>
+        <v>6385429</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
         <v>128923521</v>
       </c>
       <c r="B6" t="n">
-        <v>98726</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128923514</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>92836</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128923518</v>
+        <v>128923516</v>
       </c>
       <c r="B9" t="n">
         <v>86995</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726205</v>
+        <v>726321</v>
       </c>
       <c r="R9" t="n">
-        <v>6385310</v>
+        <v>6385413</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,7 +1475,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128923520</v>
+        <v>128923518</v>
       </c>
       <c r="B10" t="n">
         <v>86995</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726122</v>
+        <v>726205</v>
       </c>
       <c r="R10" t="n">
-        <v>6385222</v>
+        <v>6385310</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128923516</v>
+        <v>128923520</v>
       </c>
       <c r="B11" t="n">
         <v>86995</v>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726321</v>
+        <v>726122</v>
       </c>
       <c r="R11" t="n">
-        <v>6385413</v>
+        <v>6385222</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -1093,7 +1093,7 @@
         <v>128923521</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98728</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128923524</v>
       </c>
       <c r="B3" t="n">
-        <v>87052</v>
+        <v>87055</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128923517</v>
       </c>
       <c r="B4" t="n">
-        <v>86995</v>
+        <v>86998</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>128923519</v>
       </c>
       <c r="B5" t="n">
-        <v>86995</v>
+        <v>86998</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128923521</v>
       </c>
       <c r="B6" t="n">
-        <v>98728</v>
+        <v>98732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128923514</v>
       </c>
       <c r="B7" t="n">
-        <v>92836</v>
+        <v>92839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,32 +1280,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128923525</v>
+        <v>128923516</v>
       </c>
       <c r="B8" t="n">
-        <v>86820</v>
+        <v>86998</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726310</v>
+        <v>726321</v>
       </c>
       <c r="R8" t="n">
-        <v>6385406</v>
+        <v>6385413</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,6 +1359,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1377,10 +1378,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128923516</v>
+        <v>128923518</v>
       </c>
       <c r="B9" t="n">
-        <v>86995</v>
+        <v>86998</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1412,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726321</v>
+        <v>726205</v>
       </c>
       <c r="R9" t="n">
-        <v>6385413</v>
+        <v>6385310</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128923518</v>
+        <v>128923520</v>
       </c>
       <c r="B10" t="n">
-        <v>86995</v>
+        <v>86998</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1510,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726205</v>
+        <v>726122</v>
       </c>
       <c r="R10" t="n">
-        <v>6385310</v>
+        <v>6385222</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,32 +1574,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128923520</v>
+        <v>128923525</v>
       </c>
       <c r="B11" t="n">
-        <v>86995</v>
+        <v>86823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726122</v>
+        <v>726310</v>
       </c>
       <c r="R11" t="n">
-        <v>6385222</v>
+        <v>6385406</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1652,7 +1653,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>128923526</v>
       </c>
       <c r="B12" t="n">
-        <v>86820</v>
+        <v>86823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>128923528</v>
       </c>
       <c r="B13" t="n">
-        <v>86820</v>
+        <v>86823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>128923530</v>
       </c>
       <c r="B14" t="n">
-        <v>86958</v>
+        <v>86961</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -1280,32 +1280,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128923516</v>
+        <v>128923525</v>
       </c>
       <c r="B8" t="n">
-        <v>86998</v>
+        <v>86823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726321</v>
+        <v>726310</v>
       </c>
       <c r="R8" t="n">
-        <v>6385413</v>
+        <v>6385406</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1359,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1378,7 +1377,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128923518</v>
+        <v>128923516</v>
       </c>
       <c r="B9" t="n">
         <v>86998</v>
@@ -1413,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726205</v>
+        <v>726321</v>
       </c>
       <c r="R9" t="n">
-        <v>6385310</v>
+        <v>6385413</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,7 +1475,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128923520</v>
+        <v>128923518</v>
       </c>
       <c r="B10" t="n">
         <v>86998</v>
@@ -1511,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726122</v>
+        <v>726205</v>
       </c>
       <c r="R10" t="n">
-        <v>6385222</v>
+        <v>6385310</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,32 +1573,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128923525</v>
+        <v>128923520</v>
       </c>
       <c r="B11" t="n">
-        <v>86823</v>
+        <v>86998</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726310</v>
+        <v>726122</v>
       </c>
       <c r="R11" t="n">
-        <v>6385406</v>
+        <v>6385222</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,6 +1652,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -800,30 +800,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128923524</v>
+        <v>128923517</v>
       </c>
       <c r="B3" t="n">
-        <v>87055</v>
+        <v>87000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>726121</v>
+        <v>726207</v>
       </c>
       <c r="R3" t="n">
-        <v>6385220</v>
+        <v>6385429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,34 +898,30 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128923517</v>
+        <v>128923524</v>
       </c>
       <c r="B4" t="n">
-        <v>86998</v>
+        <v>87057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>726207</v>
+        <v>726121</v>
       </c>
       <c r="R4" t="n">
-        <v>6385429</v>
+        <v>6385220</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +995,7 @@
         <v>128923519</v>
       </c>
       <c r="B5" t="n">
-        <v>86998</v>
+        <v>87000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128923521</v>
       </c>
       <c r="B6" t="n">
-        <v>98732</v>
+        <v>98734</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128923514</v>
       </c>
       <c r="B7" t="n">
-        <v>92839</v>
+        <v>92841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128923525</v>
       </c>
       <c r="B8" t="n">
-        <v>86823</v>
+        <v>86825</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>128923516</v>
       </c>
       <c r="B9" t="n">
-        <v>86998</v>
+        <v>87000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128923518</v>
       </c>
       <c r="B10" t="n">
-        <v>86998</v>
+        <v>87000</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>128923520</v>
       </c>
       <c r="B11" t="n">
-        <v>86998</v>
+        <v>87000</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>128923526</v>
       </c>
       <c r="B12" t="n">
-        <v>86823</v>
+        <v>86825</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>128923528</v>
       </c>
       <c r="B13" t="n">
-        <v>86823</v>
+        <v>86825</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>128923530</v>
       </c>
       <c r="B14" t="n">
-        <v>86961</v>
+        <v>86963</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -800,34 +800,30 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128923517</v>
+        <v>128923524</v>
       </c>
       <c r="B3" t="n">
-        <v>87000</v>
+        <v>87061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>726207</v>
+        <v>726121</v>
       </c>
       <c r="R3" t="n">
-        <v>6385429</v>
+        <v>6385220</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,30 +894,34 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128923524</v>
+        <v>128923517</v>
       </c>
       <c r="B4" t="n">
-        <v>87057</v>
+        <v>87004</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>726121</v>
+        <v>726207</v>
       </c>
       <c r="R4" t="n">
-        <v>6385220</v>
+        <v>6385429</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +995,7 @@
         <v>128923519</v>
       </c>
       <c r="B5" t="n">
-        <v>87000</v>
+        <v>87004</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128923521</v>
       </c>
       <c r="B6" t="n">
-        <v>98734</v>
+        <v>98738</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128923514</v>
       </c>
       <c r="B7" t="n">
-        <v>92841</v>
+        <v>92845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,32 +1280,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128923525</v>
+        <v>128923516</v>
       </c>
       <c r="B8" t="n">
-        <v>86825</v>
+        <v>87004</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726310</v>
+        <v>726321</v>
       </c>
       <c r="R8" t="n">
-        <v>6385406</v>
+        <v>6385413</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,6 +1359,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1377,10 +1378,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128923516</v>
+        <v>128923518</v>
       </c>
       <c r="B9" t="n">
-        <v>87000</v>
+        <v>87004</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1412,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726321</v>
+        <v>726205</v>
       </c>
       <c r="R9" t="n">
-        <v>6385413</v>
+        <v>6385310</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128923518</v>
+        <v>128923520</v>
       </c>
       <c r="B10" t="n">
-        <v>87000</v>
+        <v>87004</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1510,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726205</v>
+        <v>726122</v>
       </c>
       <c r="R10" t="n">
-        <v>6385310</v>
+        <v>6385222</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,32 +1574,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128923520</v>
+        <v>128923525</v>
       </c>
       <c r="B11" t="n">
-        <v>87000</v>
+        <v>86829</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726122</v>
+        <v>726310</v>
       </c>
       <c r="R11" t="n">
-        <v>6385222</v>
+        <v>6385406</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1652,7 +1653,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>128923526</v>
       </c>
       <c r="B12" t="n">
-        <v>86825</v>
+        <v>86829</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>128923528</v>
       </c>
       <c r="B13" t="n">
-        <v>86825</v>
+        <v>86829</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>128923530</v>
       </c>
       <c r="B14" t="n">
-        <v>86963</v>
+        <v>86967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,155 +675,128 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127905051</v>
+        <v>128923524</v>
       </c>
       <c r="B2" t="n">
-        <v>56620</v>
+        <v>87403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100053</v>
+        <v>433</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gotlands kommun, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>726210</v>
+        <v>726121</v>
       </c>
       <c r="R2" t="n">
-        <v>6385246</v>
+        <v>6385220</v>
       </c>
       <c r="S2" t="n">
+        <v>10</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="b">
         <v>1</v>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Gothem</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>22:31</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>22:31</t>
-        </is>
-      </c>
-      <c r="AD2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Möller</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Möller</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>WWF - Tillsammans för Sveriges igelkottar</t>
-        </is>
-      </c>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128923524</v>
+        <v>128923530</v>
       </c>
       <c r="B3" t="n">
-        <v>87061</v>
+        <v>87309</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>433</v>
+        <v>3674</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,10 +804,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>726121</v>
+        <v>726161</v>
       </c>
       <c r="R3" t="n">
-        <v>6385220</v>
+        <v>6385253</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,9 +846,8 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -894,10 +866,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128923517</v>
+        <v>128923525</v>
       </c>
       <c r="B4" t="n">
-        <v>87004</v>
+        <v>87170</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +877,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +901,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>726207</v>
+        <v>726310</v>
       </c>
       <c r="R4" t="n">
-        <v>6385429</v>
+        <v>6385406</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +945,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -992,10 +963,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128923519</v>
+        <v>128923526</v>
       </c>
       <c r="B5" t="n">
-        <v>87004</v>
+        <v>87170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,21 +974,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,7 +1001,7 @@
         <v>726201</v>
       </c>
       <c r="R5" t="n">
-        <v>6385293</v>
+        <v>6385286</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1042,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1090,32 +1060,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128923521</v>
+        <v>128923528</v>
       </c>
       <c r="B6" t="n">
-        <v>98738</v>
+        <v>87170</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>3712</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1125,10 +1095,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>726187</v>
+        <v>726191</v>
       </c>
       <c r="R6" t="n">
-        <v>6385421</v>
+        <v>6385286</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,30 +1157,34 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128923514</v>
+        <v>128923529</v>
       </c>
       <c r="B7" t="n">
-        <v>92845</v>
+        <v>87170</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6047725</v>
+        <v>3712</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1218,10 +1192,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>726206</v>
+        <v>726031</v>
       </c>
       <c r="R7" t="n">
-        <v>6385308</v>
+        <v>6385213</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,48 +1254,62 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128923516</v>
+        <v>127905051</v>
       </c>
       <c r="B8" t="n">
-        <v>87004</v>
+        <v>56845</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>100053</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Gotlands kommun, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726321</v>
+        <v>726210</v>
       </c>
       <c r="R8" t="n">
-        <v>6385413</v>
+        <v>6385246</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1345,12 +1333,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,51 +1357,54 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Johan Möller</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Via Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128923518</v>
+        <v>128923521</v>
       </c>
       <c r="B9" t="n">
-        <v>87004</v>
+        <v>99141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6003295</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1413,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726205</v>
+        <v>726187</v>
       </c>
       <c r="R9" t="n">
-        <v>6385310</v>
+        <v>6385421</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1457,7 +1458,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128923520</v>
+        <v>128923516</v>
       </c>
       <c r="B10" t="n">
-        <v>87004</v>
+        <v>87346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726122</v>
+        <v>726321</v>
       </c>
       <c r="R10" t="n">
-        <v>6385222</v>
+        <v>6385413</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,32 +1574,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128923525</v>
+        <v>128923517</v>
       </c>
       <c r="B11" t="n">
-        <v>86829</v>
+        <v>87346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726310</v>
+        <v>726207</v>
       </c>
       <c r="R11" t="n">
-        <v>6385406</v>
+        <v>6385429</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,6 +1653,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1671,32 +1672,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128923526</v>
+        <v>128923518</v>
       </c>
       <c r="B12" t="n">
-        <v>86829</v>
+        <v>87346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1706,10 +1707,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>726201</v>
+        <v>726205</v>
       </c>
       <c r="R12" t="n">
-        <v>6385286</v>
+        <v>6385310</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,6 +1751,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1768,32 +1770,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128923528</v>
+        <v>128923519</v>
       </c>
       <c r="B13" t="n">
-        <v>86829</v>
+        <v>87346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1803,10 +1805,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>726191</v>
+        <v>726201</v>
       </c>
       <c r="R13" t="n">
-        <v>6385286</v>
+        <v>6385293</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,6 +1849,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1865,32 +1868,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128923530</v>
+        <v>128923520</v>
       </c>
       <c r="B14" t="n">
-        <v>86967</v>
+        <v>87346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1900,10 +1903,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>726161</v>
+        <v>726122</v>
       </c>
       <c r="R14" t="n">
-        <v>6385253</v>
+        <v>6385222</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,6 +1947,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1959,6 +1963,99 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128923514</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93211</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>726206</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6385308</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34142-2024 artfynd.xlsx
+++ b/artfynd/A 34142-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -766,6 +771,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128923524</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -863,6 +873,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128923530</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -960,6 +975,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128923525</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1057,6 +1077,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128923526</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1154,6 +1179,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128923528</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1251,6 +1281,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128923529</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127905051</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128923521</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1571,6 +1616,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128923516</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1669,6 +1719,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128923517</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1767,6 +1822,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128923518</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1865,6 +1925,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128923519</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1963,6 +2028,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128923520</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2056,8 +2126,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128923514</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>